--- a/UI/data/database_pasien.xlsx
+++ b/UI/data/database_pasien.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="65">
   <si>
     <t>usia</t>
   </si>
@@ -194,6 +194,21 @@
   </si>
   <si>
     <t>2025-12-15 07:08:10</t>
+  </si>
+  <si>
+    <t>2026-01-12 15:12:15</t>
+  </si>
+  <si>
+    <t>2026-01-12 15:12:29</t>
+  </si>
+  <si>
+    <t>2026-01-12 15:12:55</t>
+  </si>
+  <si>
+    <t>2026-01-12 15:13:08</t>
+  </si>
+  <si>
+    <t>2026-01-12 15:43:36</t>
   </si>
 </sst>
 </file>
@@ -551,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -2619,6 +2634,301 @@
         <v>34</v>
       </c>
     </row>
+    <row r="36" spans="1:19">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>33.3</v>
+      </c>
+      <c r="C36">
+        <v>129</v>
+      </c>
+      <c r="D36">
+        <v>87</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36">
+        <v>10.9</v>
+      </c>
+      <c r="H36">
+        <v>3.2</v>
+      </c>
+      <c r="I36">
+        <v>8.6</v>
+      </c>
+      <c r="J36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" t="s">
+        <v>22</v>
+      </c>
+      <c r="L36" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" t="s">
+        <v>24</v>
+      </c>
+      <c r="O36">
+        <v>0.6119605000716999</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0.6242858358137171</v>
+      </c>
+      <c r="R36" t="s">
+        <v>60</v>
+      </c>
+      <c r="S36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>33.3</v>
+      </c>
+      <c r="C37">
+        <v>135</v>
+      </c>
+      <c r="D37">
+        <v>87</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37">
+        <v>10.9</v>
+      </c>
+      <c r="H37">
+        <v>3.2</v>
+      </c>
+      <c r="I37">
+        <v>8.6</v>
+      </c>
+      <c r="J37" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" t="s">
+        <v>25</v>
+      </c>
+      <c r="O37">
+        <v>0.6435774989637869</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <v>0.6242858358137171</v>
+      </c>
+      <c r="R37" t="s">
+        <v>61</v>
+      </c>
+      <c r="S37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38">
+        <v>25</v>
+      </c>
+      <c r="B38">
+        <v>30.3</v>
+      </c>
+      <c r="C38">
+        <v>135</v>
+      </c>
+      <c r="D38">
+        <v>87</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38">
+        <v>10.9</v>
+      </c>
+      <c r="H38">
+        <v>3.2</v>
+      </c>
+      <c r="I38">
+        <v>8.6</v>
+      </c>
+      <c r="J38" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" t="s">
+        <v>22</v>
+      </c>
+      <c r="L38" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" t="s">
+        <v>24</v>
+      </c>
+      <c r="O38">
+        <v>0.6206621800031651</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0.6242858358137171</v>
+      </c>
+      <c r="R38" t="s">
+        <v>62</v>
+      </c>
+      <c r="S38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39">
+        <v>25</v>
+      </c>
+      <c r="B39">
+        <v>30.3</v>
+      </c>
+      <c r="C39">
+        <v>140</v>
+      </c>
+      <c r="D39">
+        <v>87</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39">
+        <v>10.9</v>
+      </c>
+      <c r="H39">
+        <v>3.2</v>
+      </c>
+      <c r="I39">
+        <v>8.6</v>
+      </c>
+      <c r="J39" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" t="s">
+        <v>25</v>
+      </c>
+      <c r="O39">
+        <v>0.6585071585980135</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39">
+        <v>0.6242858358137171</v>
+      </c>
+      <c r="R39" t="s">
+        <v>63</v>
+      </c>
+      <c r="S39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40">
+        <v>35</v>
+      </c>
+      <c r="B40">
+        <v>33.3</v>
+      </c>
+      <c r="C40">
+        <v>139</v>
+      </c>
+      <c r="D40">
+        <v>87</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40">
+        <v>10.9</v>
+      </c>
+      <c r="H40">
+        <v>3.2</v>
+      </c>
+      <c r="I40">
+        <v>8.6</v>
+      </c>
+      <c r="J40" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40" t="s">
+        <v>22</v>
+      </c>
+      <c r="N40" t="s">
+        <v>25</v>
+      </c>
+      <c r="O40">
+        <v>0.6660852506939186</v>
+      </c>
+      <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="Q40">
+        <v>0.6242858358137171</v>
+      </c>
+      <c r="R40" t="s">
+        <v>64</v>
+      </c>
+      <c r="S40">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
